--- a/excel/pacifico-dex-sociedad-anonima-cerrada_efectivos.xlsx
+++ b/excel/pacifico-dex-sociedad-anonima-cerrada_efectivos.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C000881847</t>
+          <t>C000875926</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C000881847 - GUILLEN BENDEZU VIRGILIO EARLY</t>
+          <t>C000875926 - QUISPE CACERES DORIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -597,13 +597,25 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No desea</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -628,12 +640,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C001362233</t>
+          <t>C000881847</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001362233 - SAAVEDRA SOTO JAVIER YSIDRO</t>
+          <t>C000881847 - GUILLEN BENDEZU VIRGILIO EARLY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -662,25 +674,13 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C000877630</t>
+          <t>C001362233</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C000877630 - BULEJE ELIZALDE CARMEN</t>
+          <t>C001362233 - SAAVEDRA SOTO JAVIER YSIDRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -739,13 +739,25 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -835,12 +847,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C004016410</t>
+          <t>C001552894</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C004016410 - MUCHAYPIÑA MEDINA BERTHA HERLINDA</t>
+          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -912,12 +924,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C000875926</t>
+          <t>C000877630</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C000875926 - QUISPE CACERES DORIS</t>
+          <t>C000877630 - BULEJE ELIZALDE CARMEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -946,25 +958,13 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C001552894</t>
+          <t>C000877206</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
+          <t>C000877206 - MENDOZA RODRIGUEZ ROSA ISABEL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1027,21 +1027,9 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1066,12 +1054,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C000881069</t>
+          <t>C001492590</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C000881069 - PEREZ MORAN JULIO FELIX</t>
+          <t>C001492590 - QUISPE HUAYHUAS MONICA GENOVEVA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1100,25 +1088,13 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1143,12 +1119,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C000882088</t>
+          <t>C001715921</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C000882088 - BRAVO DE ANGULO LIDIA</t>
+          <t>C001715921 - APARCANA PISCONTE LUIS ANTONIO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1177,13 +1153,25 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1208,12 +1196,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C000876112</t>
+          <t>C001737288</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C000876112 - GAVILAN RAMOS NANCY</t>
+          <t>C001737288 - ANTEZANA MENDOZA SILVIA NANCY</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1245,7 +1233,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -1285,12 +1277,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C001715921</t>
+          <t>C000881069</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001715921 - APARCANA PISCONTE LUIS ANTONIO</t>
+          <t>C000881069 - PEREZ MORAN JULIO FELIX</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1362,12 +1354,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C001737288</t>
+          <t>C000882088</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001737288 - ANTEZANA MENDOZA SILVIA NANCY</t>
+          <t>C000882088 - BRAVO DE ANGULO LIDIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1396,29 +1388,13 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1443,17 +1419,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C000877206</t>
+          <t>C001733616</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C000877206 - MENDOZA RODRIGUEZ ROSA ISABEL</t>
+          <t>C001733616 - RUEDA GARCIA CECILIA JESSICA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1466,12 +1442,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1481,9 +1457,21 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1508,12 +1496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C001492590</t>
+          <t>C000876112</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001492590 - QUISPE HUAYHUAS MONICA GENOVEVA</t>
+          <t>C000876112 - GAVILAN RAMOS NANCY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1542,13 +1530,25 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>No desea</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C001733616</t>
+          <t>C001736860</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001733616 - RUEDA GARCIA CECILIA JESSICA</t>
+          <t>C001736860 - PUPPI DE GALLEGOS RODELINDA ALEJANDRINA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C001736860</t>
+          <t>C004016410</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001736860 - PUPPI DE GALLEGOS RODELINDA ALEJANDRINA</t>
+          <t>C004016410 - MUCHAYPIÑA MEDINA BERTHA HERLINDA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1999,17 +1999,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C000877090</t>
+          <t>C004205633</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
+          <t>C004205633 -  PARIONA ESPINOZA LUIS ALBERTO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2037,21 +2037,9 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2076,12 +2064,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C004218241</t>
+          <t>C000877090</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004218241 - BARRIOS VALLEJOS FLOR DE MARIA</t>
+          <t>C000877090 - UCULMANA ANICAMA PILAR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2110,17 +2098,25 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>No deja trabajar</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2145,17 +2141,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C004205633</t>
+          <t>C004218241</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004205633 -  PARIONA ESPINOZA LUIS ALBERTO</t>
+          <t>C004218241 - BARRIOS VALLEJOS FLOR DE MARIA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -2168,21 +2164,25 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>No deja trabajar</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>C001748916</t>
+          <t>C004223837</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
+          <t>C004223837 - MAVILA ALVAREZ WALTER WILFREDO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>C004203039</t>
+          <t>C001748916</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C004203039 - QUINTANILLA YALLE CARMEN NANCY</t>
+          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>C004223837</t>
+          <t>C004203039</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C004223837 - MAVILA ALVAREZ WALTER WILFREDO</t>
+          <t>C004203039 - QUINTANILLA YALLE CARMEN NANCY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C004036828</t>
+          <t>C004032075</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004036828 - QUISPE SANCHEZ ANGELICA MARIA</t>
+          <t>C004032075 - DISTRIBUIDORA COMERCIAL ALBITES S.A.C.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2941,9 +2941,21 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2968,17 +2980,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C004032075</t>
+          <t>C004036828</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C004032075 - DISTRIBUIDORA COMERCIAL ALBITES S.A.C.</t>
+          <t>C004036828 - QUISPE SANCHEZ ANGELICA MARIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -2991,12 +3003,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -3006,21 +3018,9 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C004179220</t>
+          <t>C004014091</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C004179220 - ESCALANTE QUIHUE MARITZA PELAGIA</t>
+          <t>C004014091 - DISTRIBUIDORA JOSUE &amp; DAVID E.I.R.L.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C001672172</t>
+          <t>C004179220</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001672172 - TENORIO SORIA LILY AMPARO</t>
+          <t>C004179220 - ESCALANTE QUIHUE MARITZA PELAGIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>C001731742</t>
+          <t>C001733058</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001731742 - AUQUES ZARATE JACKELYNE</t>
+          <t>C001733058 - HUAMAN ANDRES MERCEDES DALILA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3391,9 +3391,21 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3418,12 +3430,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>C000872477</t>
+          <t>C001672172</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
+          <t>C001672172 - TENORIO SORIA LILY AMPARO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3572,12 +3584,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>C001733058</t>
+          <t>C000872477</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001733058 - HUAMAN ANDRES MERCEDES DALILA</t>
+          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3649,17 +3661,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>C001580075</t>
+          <t>C001731742</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001580075 - PAYTAN CABALLA GULIANA SALLY</t>
+          <t>C001731742 - AUQUES ZARATE JACKELYNE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -3672,12 +3684,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3687,21 +3699,9 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>C001489096</t>
+          <t>C001580075</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001489096 - AGUADO CHANCO GIOVANNA ESTHER</t>
+          <t>C001580075 - PAYTAN CABALLA GULIANA SALLY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>C001494647</t>
+          <t>C001399017</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001494647 - QUISPE CARHUAYO MARIANA MAITE</t>
+          <t>C001399017 - LLOCCLLA HUARANCCA JOSE LUIS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3957,17 +3957,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>C001657060</t>
+          <t>C001442238</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001657060 - URIBE MITACC MARIA MAGDALENA</t>
+          <t>C001442238 - ENCALADA CRISOSTOMO MARIA GLORIA ESPERAN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3995,21 +3995,9 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4034,17 +4022,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>C001641580</t>
+          <t>C001480904</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001641580 - QUISPE PILCO FELIX ALBERTO</t>
+          <t>C001480904 - GUEVARA PARADO ZOILA DIANA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -4057,12 +4045,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4072,21 +4060,9 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4111,12 +4087,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>C000880953</t>
+          <t>C001657060</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C000880953 - VILCA DE AMARCANQUI ANTONIA</t>
+          <t>C001657060 - URIBE MITACC MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4151,17 +4127,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -4188,12 +4164,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C001174355</t>
+          <t>C000880953</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001174355 - HUAMAN PALLIN JHON YSACC</t>
+          <t>C000880953 - VILCA DE AMARCANQUI ANTONIA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4228,17 +4204,17 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4241,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>C000881921</t>
+          <t>C001174355</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C000881921 - MEZA MENESES ARESTINA LIDIA</t>
+          <t>C001174355 - HUAMAN PALLIN JHON YSACC</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4299,17 +4275,25 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tercera edad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4334,17 +4318,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>C000872544</t>
+          <t>C000881921</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C000872544 - LEVANO LOPEZ MARTHA</t>
+          <t>C000881921 - MEZA MENESES ARESTINA LIDIA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -4357,21 +4341,25 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>Tercera edad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -4399,17 +4387,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>C004014091</t>
+          <t>C000872544</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C004014091 - DISTRIBUIDORA JOSUE &amp; DAVID E.I.R.L.</t>
+          <t>C000872544 - LEVANO LOPEZ MARTHA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -4422,12 +4410,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4437,21 +4425,9 @@
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4476,12 +4452,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>C000874079</t>
+          <t>C001641580</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C000874079 - ARMACANQUI VENTURA EDGAR</t>
+          <t>C001641580 - QUISPE PILCO FELIX ALBERTO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4553,17 +4529,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>C001323271</t>
+          <t>C000874079</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001323271 - GARCIA SERNA RUTH LILIANA</t>
+          <t>C000874079 - ARMACANQUI VENTURA EDGAR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -4576,12 +4552,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4591,9 +4567,21 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4618,17 +4606,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>C001398064</t>
+          <t>C001323271</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001398064 - PEREZ GUTIERREZ EDGAR ELIAS</t>
+          <t>C001323271 - GARCIA SERNA RUTH LILIANA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -4641,12 +4629,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4656,21 +4644,9 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4695,12 +4671,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>C001399017</t>
+          <t>C001398064</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C001399017 - LLOCCLLA HUARANCCA JOSE LUIS</t>
+          <t>C001398064 - PEREZ GUTIERREZ EDGAR ELIAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4772,17 +4748,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>C001442238</t>
+          <t>C001489096</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001442238 - ENCALADA CRISOSTOMO MARIA GLORIA ESPERAN</t>
+          <t>C001489096 - AGUADO CHANCO GIOVANNA ESTHER</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -4795,12 +4771,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4810,9 +4786,21 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4837,17 +4825,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>C001480904</t>
+          <t>C001494647</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001480904 - GUEVARA PARADO ZOILA DIANA</t>
+          <t>C001494647 - QUISPE CARHUAYO MARIANA MAITE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
@@ -4860,12 +4848,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4875,9 +4863,21 @@
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>C000881032</t>
+          <t>C001650094</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
+          <t>C001650094 - PUPPI DE RAMOS REYNA FIDELA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>C001650094</t>
+          <t>C001675881</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001650094 - PUPPI DE RAMOS REYNA FIDELA</t>
+          <t>C001675881 - MALDONADO DE VASQUEZ FANI ANITA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>C001675881</t>
+          <t>C001682236</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001675881 - MALDONADO DE VASQUEZ FANI ANITA</t>
+          <t>C001682236 - JURADO ACUNA NURIA MAGJURI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>C001682236</t>
+          <t>C000875215</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001682236 - JURADO ACUNA NURIA MAGJURI</t>
+          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>C000875215</t>
+          <t>C000881032</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C000875215 - QUISPE ATOCCSA CARMEN FAUSTINA</t>
+          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>C001749956</t>
+          <t>C001218162</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001749956 - LOAYZA AYBAR CARLOS ALBERTO</t>
+          <t>C001218162 - AVENTURAS Y TURISMO DEL SUR SOCIEDAD ANO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5763,21 +5763,9 @@
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5802,12 +5790,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>C001690491</t>
+          <t>C001274439</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001690491 - ANTONIO VENTURA NARCISA MARCELINA</t>
+          <t>C001274439 - MORAN QUINTANILLA VICTORIA BEBELU</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5836,13 +5824,25 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>No desea</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5867,17 +5867,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>C001218162</t>
+          <t>C001397748</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001218162 - AVENTURAS Y TURISMO DEL SUR SOCIEDAD ANO</t>
+          <t>C001397748 - RAMOS ESPINO LUZ ANGELICA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
@@ -5890,21 +5890,25 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>No desea</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
@@ -6009,12 +6013,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>C000883040</t>
+          <t>C000882225</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C000883040 - YALLE CASAVILCA NELIO</t>
+          <t>C000882225 - SAMANIEGO FRANCO ROSA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6043,25 +6047,17 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>No deseq</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6086,12 +6082,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>C000882225</t>
+          <t>C000883040</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C000882225 - SAMANIEGO FRANCO ROSA</t>
+          <t>C000883040 - YALLE CASAVILCA NELIO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6120,17 +6116,25 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>No deseq</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6155,12 +6159,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>C001397748</t>
+          <t>C001372541</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001397748 - RAMOS ESPINO LUZ ANGELICA</t>
+          <t>C001372541 - CRUZADO BENDEZU JOSE FROILAN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6189,17 +6193,25 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>No desea</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6224,12 +6236,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>C001372541</t>
+          <t>C001749956</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001372541 - CRUZADO BENDEZU JOSE FROILAN</t>
+          <t>C001749956 - LOAYZA AYBAR CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6301,12 +6313,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>C001274439</t>
+          <t>C001690491</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C001274439 - MORAN QUINTANILLA VICTORIA BEBELU</t>
+          <t>C001690491 - ANTONIO VENTURA NARCISA MARCELINA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6335,25 +6347,13 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6378,17 +6378,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>C004142346</t>
+          <t>C001707468</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C004142346 - HUAMANI MUNIVE DICK GAEL</t>
+          <t>C001707468 - LOPEZ VILLARROEL VIVIANA GLADIS</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6416,9 +6416,21 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6443,12 +6455,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>C004165676</t>
+          <t>C001736862</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C004165676 - FLORES LUNA NIDIA LORENA</t>
+          <t>C001736862 - TIRADO LOPEZ VIVIANA LIZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6520,12 +6532,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>C001707468</t>
+          <t>C000875219</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C001707468 - LOPEZ VILLARROEL VIVIANA GLADIS</t>
+          <t>C000875219 - ROMAN VILCAS MARIA MONICA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6554,25 +6566,13 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tercera.edad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>C001736862</t>
+          <t>C001443020</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C001736862 - TIRADO LOPEZ VIVIANA LIZ</t>
+          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>C004030181</t>
+          <t>C001721401</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C004030181 - VENTURA MEDRANO RUT REBECA</t>
+          <t>C001721401 - CARLOS FAJARDO MARTHA FELICITA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>C004054129</t>
+          <t>C004030181</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C004054129 - HUANCAHUARI BENDEZU LUIS FELIPE</t>
+          <t>C004030181 - VENTURA MEDRANO RUT REBECA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>C001721401</t>
+          <t>C004054129</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C001721401 - CARLOS FAJARDO MARTHA FELICITA</t>
+          <t>C004054129 - HUANCAHUARI BENDEZU LUIS FELIPE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>C000875219</t>
+          <t>C004165676</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C000875219 - ROMAN VILCAS MARIA MONICA</t>
+          <t>C004165676 - FLORES LUNA NIDIA LORENA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6939,13 +6939,25 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tercera.edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6970,17 +6982,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>C001443020</t>
+          <t>C004142346</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C001443020 - MOSQUEIRA MARCANI ROSA JUANA</t>
+          <t>C004142346 - HUAMANI MUNIVE DICK GAEL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
@@ -6993,12 +7005,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -7008,21 +7020,9 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>C004030175</t>
+          <t>C001360989</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004030175 - ESPINOZA PACHECO ZOILA CARMEN ELENINHA</t>
+          <t>C001360989 - CONISLLA CHIRA MARINA JESUS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>C001360989</t>
+          <t>C001754687</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001360989 - CONISLLA CHIRA MARINA JESUS</t>
+          <t>C001754687 - SERPA FUENTES MAXIMILIANA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>C001749432</t>
+          <t>C004030175</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001749432 - AURIS AYBAR SONIA MIRTHA</t>
+          <t>C004030175 - ESPINOZA PACHECO ZOILA CARMEN ELENINHA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>C001754687</t>
+          <t>C001749432</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001754687 - SERPA FUENTES MAXIMILIANA</t>
+          <t>C001749432 - AURIS AYBAR SONIA MIRTHA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>C000881234</t>
+          <t>C001493960</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C000881234 - LOVERA DE ROMAN NATALIA</t>
+          <t>C001493960 - CHAVEZ PEREZ MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
@@ -7508,25 +7508,21 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>P3rsona tercera edad</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
@@ -7554,17 +7550,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>C000881044</t>
+          <t>C001168915</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C000881044 - CHANG PURILLA VICTOR JESUS</t>
+          <t>C001168915 - MANTARI HUAMANI ADELAIDA EMERITA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
@@ -7577,18 +7573,18 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No deja trabajar</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -7619,12 +7615,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>C001168915</t>
+          <t>C001502263</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001168915 - MANTARI HUAMANI ADELAIDA EMERITA</t>
+          <t>C001502263 - MATTA ROMERO MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7653,13 +7649,25 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>No deja trabajar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7684,12 +7692,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>C001502263</t>
+          <t>C000881234</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001502263 - MATTA ROMERO MIGUEL ANGEL</t>
+          <t>C000881234 - LOVERA DE ROMAN NATALIA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7718,25 +7726,17 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+          <t>P3rsona tercera edad</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7761,17 +7761,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>C000874090</t>
+          <t>C000881044</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C000874090 - CABEZUDO BERNAOLA FRED</t>
+          <t>C000881044 - CHANG PURILLA VICTOR JESUS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7799,21 +7799,9 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7838,12 +7826,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>C001376387</t>
+          <t>C000874090</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C001376387 - GARCIA GARIBAY MIRIAM MARLENE</t>
+          <t>C000874090 - CABEZUDO BERNAOLA FRED</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7992,12 +7980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>C001494780</t>
+          <t>C001376387</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001494780 - PALOMINO ALVARADO DIONICIA</t>
+          <t>C001376387 - GARCIA GARIBAY MIRIAM MARLENE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8069,12 +8057,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>C001489093</t>
+          <t>C001494780</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001489093 - EVANAN PAUCAR NANCY PILAR</t>
+          <t>C001494780 - PALOMINO ALVARADO DIONICIA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8146,17 +8134,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>C001493960</t>
+          <t>C001489093</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001493960 - CHAVEZ PEREZ MIGUEL ANGEL</t>
+          <t>C001489093 - EVANAN PAUCAR NANCY PILAR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
@@ -8169,12 +8157,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -8184,9 +8172,21 @@
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>C000878065</t>
+          <t>C001678425</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C000878065 - VILCA TINEO NIEVES</t>
+          <t>C001678425 - QUINTANILLA VALDIVIA STOLLE JULIA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>C001216310</t>
+          <t>C000878065</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001216310 - VENTURA SOTO JULIA</t>
+          <t>C000878065 - VILCA TINEO NIEVES</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>C001678425</t>
+          <t>C001216310</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C001678425 - QUINTANILLA VALDIVIA STOLLE JULIA</t>
+          <t>C001216310 - VENTURA SOTO JULIA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9010,17 +9010,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>C004182379</t>
+          <t>C004044927</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C004182379 - GUERRERO ESCALANTE LUISA JULIANA</t>
+          <t>C004044927 - LLANA DE ARONI YNES</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -9048,9 +9048,21 @@
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9075,17 +9087,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>C004172308</t>
+          <t>C004182379</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C004172308 - SARMIENTO SERPA JHORCHS ANGEL</t>
+          <t>C004182379 - GUERRERO ESCALANTE LUISA JULIANA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
@@ -9098,12 +9110,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -9113,21 +9125,9 @@
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>C004044927</t>
+          <t>C004172308</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C004044927 - LLANA DE ARONI YNES</t>
+          <t>C004172308 - SARMIENTO SERPA JHORCHS ANGEL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -9229,17 +9229,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>C004242029</t>
+          <t>C004191059</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>C004242029 - GOMEZ SALINAS LEONARDO ALEXANDER</t>
+          <t>C004191059 - HUAMANI MARCOS ANA YSABEL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H120" s="2" t="n">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -9267,21 +9267,9 @@
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9306,17 +9294,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>C001714592</t>
+          <t>C004197824</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C001714592 - PEÑA GARCIA RAQUEL</t>
+          <t>C004197824 - CHOQUE OLAECHEA MARIA TERESA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
@@ -9329,12 +9317,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -9344,9 +9332,21 @@
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>C001393042</t>
+          <t>C004242029</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C001393042 - HUASASQUICHE LEGUA BLANCA LUZ</t>
+          <t>C004242029 - GOMEZ SALINAS LEONARDO ALEXANDER</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>C004191059</t>
+          <t>C004202089</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C004191059 - HUAMANI MARCOS ANA YSABEL</t>
+          <t>C004202089 - ARAPA HUARCA FRIDA PAULINA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -9594,17 +9594,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>C004197824</t>
+          <t>C001714592</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C004197824 - CHOQUE OLAECHEA MARIA TERESA</t>
+          <t>C001714592 - PEÑA GARCIA RAQUEL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H125" s="2" t="n">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -9632,21 +9632,9 @@
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9736,17 +9724,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>C004236590</t>
+          <t>C001393042</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C004236590 - ESPINO LUJAN MERY GUICELA</t>
+          <t>C001393042 - HUASASQUICHE LEGUA BLANCA LUZ</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H127" s="2" t="n">
@@ -9759,12 +9747,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -9774,9 +9762,21 @@
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9801,17 +9801,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>C004203440</t>
+          <t>C004236590</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C004203440 - HERNANDEZ DONAYRE CONSUELO HAYDEE</t>
+          <t>C004236590 - ESPINO LUJAN MERY GUICELA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H128" s="2" t="n">
@@ -9824,25 +9824,21 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>No tiene celular</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
@@ -9870,17 +9866,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>C004202089</t>
+          <t>C004203440</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C004202089 - ARAPA HUARCA FRIDA PAULINA</t>
+          <t>C004203440 - HERNANDEZ DONAYRE CONSUELO HAYDEE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H129" s="2" t="n">
@@ -9893,21 +9889,25 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
+          <t>No tiene celular</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
@@ -9935,17 +9935,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>C000880873</t>
+          <t>C000882635</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C000880873 - ALTAMIRANO TINEO JORGE LUIS</t>
+          <t>C000882635 - ORTIZ CABRERA YULY SUSAN</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H130" s="2" t="n">
@@ -9958,12 +9958,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -9973,21 +9973,9 @@
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10012,12 +10000,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>C000882635</t>
+          <t>C001505733</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C000882635 - ORTIZ CABRERA YULY SUSAN</t>
+          <t>C001505733 - PARIONA MALDONADO CLETA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -10077,17 +10065,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>C001505733</t>
+          <t>C000880873</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C001505733 - PARIONA MALDONADO CLETA</t>
+          <t>C000880873 - ALTAMIRANO TINEO JORGE LUIS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H132" s="2" t="n">
@@ -10100,12 +10088,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -10115,9 +10103,21 @@
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>C000881763</t>
+          <t>C001017106</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>C000881763 - GALINDO GONZALES WILLIAM</t>
+          <t>C001017106 - DIAZ BERROCAL MONICA VERONICA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>C001017106</t>
+          <t>C000881763</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C001017106 - DIAZ BERROCAL MONICA VERONICA</t>
+          <t>C000881763 - GALINDO GONZALES WILLIAM</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>C001491104</t>
+          <t>C001442207</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>C001491104 - ANGULO ESPINO MANUEL JESUS</t>
+          <t>C001442207 - HERRERA CABRERA JAIME ANTONIO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>C001744752</t>
+          <t>C001692152</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C001744752 - VIDAL FLORES NOELIA MILUSKA</t>
+          <t>C001692152 - HUAYANCA HERRERA ROSA SOLEDAD</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10438,17 +10438,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>C001569036</t>
+          <t>C001372288</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C001569036 - YALLICO MEZA KAROL AURORA</t>
+          <t>C001372288 - QUISPE DE ROMAN MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H137" s="2" t="n">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -10476,9 +10476,21 @@
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10503,12 +10515,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>C001442207</t>
+          <t>C001573215</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C001442207 - HERRERA CABRERA JAIME ANTONIO</t>
+          <t>C001573215 - DEL POZO VALENCIA LAMARQUE NIELSIN</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10580,12 +10592,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>C001692152</t>
+          <t>C001469511</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C001692152 - HUAYANCA HERRERA ROSA SOLEDAD</t>
+          <t>C001469511 - ROJAS HERNANDEZ ROSA MARIA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10645,17 +10657,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>C001372288</t>
+          <t>C001744752</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C001372288 - QUISPE DE ROMAN MARIA MAGDALENA</t>
+          <t>C001744752 - VIDAL FLORES NOELIA MILUSKA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H140" s="2" t="n">
@@ -10668,12 +10680,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -10683,21 +10695,9 @@
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>C001573215</t>
+          <t>C001491104</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>C001573215 - DEL POZO VALENCIA LAMARQUE NIELSIN</t>
+          <t>C001491104 - ANGULO ESPINO MANUEL JESUS</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>C001469511</t>
+          <t>C001569036</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C001469511 - ROJAS HERNANDEZ ROSA MARIA</t>
+          <t>C001569036 - YALLICO MEZA KAROL AURORA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10864,17 +10864,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>C001715926</t>
+          <t>C000876293</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C001715926 - CUCHO GAMBOA ETHEL JOSELYNE FLOR</t>
+          <t>C000876293 - MORAN CRUCES GLORIA</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H143" s="2" t="n">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -10902,9 +10902,21 @@
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10994,17 +11006,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>C000876293</t>
+          <t>C001444256</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C000876293 - MORAN CRUCES GLORIA</t>
+          <t>C001444256 - APARCANA PISCONTE MARIA JOVITA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H145" s="2" t="n">
@@ -11017,12 +11029,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -11032,21 +11044,9 @@
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>C001444256</t>
+          <t>C001390794</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C001444256 - APARCANA PISCONTE MARIA JOVITA</t>
+          <t>C001390794 - ARAUJO MEDINA KARINA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>C001390794</t>
+          <t>C001715926</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C001390794 - ARAUJO MEDINA KARINA</t>
+          <t>C001715926 - CUCHO GAMBOA ETHEL JOSELYNE FLOR</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11408,17 +11408,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>C001708333</t>
+          <t>C004030170</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C001708333 - ISUIZA FLORES JACKELIN LORENA</t>
+          <t>C004030170 - LOVERA SIGUAS ANA ISABEL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H151" s="2" t="n">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -11446,9 +11446,21 @@
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11473,17 +11485,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>C004030172</t>
+          <t>C004030176</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C004030172 - HILARIO ZARATE CONSUELO</t>
+          <t>C004030176 - QUISPE FLORES ELIZABETH ELENA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
@@ -11496,12 +11508,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -11511,9 +11523,21 @@
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11538,17 +11562,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>C004030170</t>
+          <t>C004030172</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C004030170 - LOVERA SIGUAS ANA ISABEL</t>
+          <t>C004030172 - HILARIO ZARATE CONSUELO</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H153" s="2" t="n">
@@ -11561,12 +11585,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -11576,21 +11600,9 @@
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11615,17 +11627,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>C004030176</t>
+          <t>C001708333</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C004030176 - QUISPE FLORES ELIZABETH ELENA</t>
+          <t>C001708333 - ISUIZA FLORES JACKELIN LORENA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H154" s="2" t="n">
@@ -11638,12 +11650,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -11653,21 +11665,9 @@
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11769,17 +11769,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>C001419656</t>
+          <t>C004030168</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C001419656 - HUANCAHUARI QUISPE VIOLETA ALINA</t>
+          <t>C004030168 - MANCHEGO AURIS YANINA NIDIA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H156" s="2" t="n">
@@ -11792,12 +11792,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -11807,9 +11807,21 @@
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11834,17 +11846,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>C000875504</t>
+          <t>C001711331</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C000875504 - CERVANTES HUAMANI ADRIAN</t>
+          <t>C001711331 - PEREZ TORREALVA JAIME GILBERTO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H157" s="2" t="n">
@@ -11857,12 +11869,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -11872,21 +11884,9 @@
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>C001561985</t>
+          <t>C001612526</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001561985 - SALAS DE ESCRIBAS CIRILA</t>
+          <t>C001612526 - CARRERA CAHUANA GERARDO JOSE</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11988,17 +11988,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>C001492921</t>
+          <t>C001286581</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C001492921 - SEDANO DE LA CRUZ SERAPIO</t>
+          <t>C001286581 - CORTEZ PEREYRA MILAGROS ESTEFANI</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H159" s="2" t="n">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -12026,21 +12026,9 @@
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12065,12 +12053,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>C001469172</t>
+          <t>C001521201</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C001469172 - CABRERA HERNANDEZ YESICA MONICA</t>
+          <t>C001521201 - CAYO DE ANTONIO MAXIMILIANA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -12093,7 +12081,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -12130,12 +12118,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>C001469510</t>
+          <t>C001740525</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C001469510 - GARCIA BARRIENTOS REBECA</t>
+          <t>C001740525 - SEDANO SULLCA GLIDER JUAN</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12180,7 +12168,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
     </row>
@@ -12207,17 +12195,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>C001440721</t>
+          <t>C001469172</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>C001440721 - CAYAMPI BARRIENTOS MARIBEL LUZ</t>
+          <t>C001469172 - CABRERA HERNANDEZ YESICA MONICA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
@@ -12230,12 +12218,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -12245,21 +12233,9 @@
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12284,17 +12260,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>C001379725</t>
+          <t>C001469510</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C001379725 - QUISPE HUAMANI ALEJANDRO</t>
+          <t>C001469510 - GARCIA BARRIENTOS REBECA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H163" s="2" t="n">
@@ -12307,12 +12283,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -12322,9 +12298,21 @@
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12349,12 +12337,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>C004030168</t>
+          <t>C000875504</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>C004030168 - MANCHEGO AURIS YANINA NIDIA</t>
+          <t>C000875504 - CERVANTES HUAMANI ADRIAN</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12426,12 +12414,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>C001711331</t>
+          <t>C001419656</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>C001711331 - PEREZ TORREALVA JAIME GILBERTO</t>
+          <t>C001419656 - HUANCAHUARI QUISPE VIOLETA ALINA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12454,7 +12442,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -12491,12 +12479,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>C001612526</t>
+          <t>C001492921</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001612526 - CARRERA CAHUANA GERARDO JOSE</t>
+          <t>C001492921 - SEDANO DE LA CRUZ SERAPIO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12568,17 +12556,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>C001286581</t>
+          <t>C001561985</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C001286581 - CORTEZ PEREYRA MILAGROS ESTEFANI</t>
+          <t>C001561985 - SALAS DE ESCRIBAS CIRILA</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H167" s="2" t="n">
@@ -12591,12 +12579,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -12606,9 +12594,21 @@
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12633,17 +12633,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>C001521201</t>
+          <t>C001440721</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C001521201 - CAYO DE ANTONIO MAXIMILIANA</t>
+          <t>C001440721 - CAYAMPI BARRIENTOS MARIBEL LUZ</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
@@ -12656,12 +12656,12 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -12671,9 +12671,21 @@
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12698,17 +12710,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>C001740525</t>
+          <t>C001379725</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C001740525 - SEDANO SULLCA GLIDER JUAN</t>
+          <t>C001379725 - QUISPE HUAMANI ALEJANDRO</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H169" s="2" t="n">
@@ -12721,12 +12733,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -12736,21 +12748,9 @@
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>Más productos disponibles</t>
-        </is>
-      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>C004142369</t>
+          <t>C001696545</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C004142369 - DOMINGUEZ VALER ELIZABETH MAGDALENA</t>
+          <t>C001696545 - LUKAMI E.I.R.L.</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>C001692262</t>
+          <t>C004142369</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C001692262 - ROJAS CHANCO IRIS MERCEDES</t>
+          <t>C004142369 - DOMINGUEZ VALER ELIZABETH MAGDALENA</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>C001696545</t>
+          <t>C001692262</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001696545 - LUKAMI E.I.R.L.</t>
+          <t>C001692262 - ROJAS CHANCO IRIS MERCEDES</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -14024,12 +14024,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>C004176459</t>
+          <t>C001735868</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C004176459 - ANGULO LEGUA TERESA CRISTINA</t>
+          <t>C001735868 - HUARCAYA SAIRITUPAC MARIA YELITZA</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14101,17 +14101,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>C004176457</t>
+          <t>C004094992</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>C004176457 - VALENZUELA GARCIA MARIA GRACIELA</t>
+          <t>C004094992 - NAPA FUENTES EDUARDO SEBASTIAN</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H188" s="2" t="n">
@@ -14124,12 +14124,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
@@ -14139,9 +14139,21 @@
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -14243,12 +14255,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>C001735868</t>
+          <t>C004176459</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C001735868 - HUARCAYA SAIRITUPAC MARIA YELITZA</t>
+          <t>C004176459 - ANGULO LEGUA TERESA CRISTINA</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14320,17 +14332,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>C004094992</t>
+          <t>C004176457</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C004094992 - NAPA FUENTES EDUARDO SEBASTIAN</t>
+          <t>C004176457 - VALENZUELA GARCIA MARIA GRACIELA</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H191" s="2" t="n">
@@ -14343,12 +14355,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -14358,21 +14370,9 @@
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -14397,12 +14397,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>C001396933</t>
+          <t>C000880815</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C001396933 - HUAMAN VALENCIA MARIELA</t>
+          <t>C000880815 - GONZALES CHANCO RUFINO</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>C000880815</t>
+          <t>C001488243</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C000880815 - GONZALES CHANCO RUFINO</t>
+          <t>C001488243 - HUAMANI MEDINA YOLANDA</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>C001488243</t>
+          <t>C001396933</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C001488243 - HUAMANI MEDINA YOLANDA</t>
+          <t>C001396933 - HUAMAN VALENCIA MARIELA</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>C001112679</t>
+          <t>C001654334</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C001112679 - CAMPOS CORONADO HILDA MAXIMA</t>
+          <t>C001654334 - HILARIO PARIONA NERY PAULINA</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -14782,12 +14782,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>C001716455</t>
+          <t>C001112679</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C001716455 - CANCHOS ALLCCA FIORELLA ALEXANDRA</t>
+          <t>C001112679 - CAMPOS CORONADO HILDA MAXIMA</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
     </row>
@@ -14859,12 +14859,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>C001654334</t>
+          <t>C001716455</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>C001654334 - HILARIO PARIONA NERY PAULINA</t>
+          <t>C001716455 - CANCHOS ALLCCA FIORELLA ALEXANDRA</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -15078,12 +15078,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>C001710029</t>
+          <t>C001428216</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C001710029 - ANCHANTE RAMIREZ ROSARIO FLORANGEL</t>
+          <t>C001428216 - MEZA MENESES NELIDA LUZ</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>C001323273</t>
+          <t>C001641578</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C001323273 - ALLCCA ZEGARRA DELIA</t>
+          <t>C001641578 - HERNANDEZ MEZA HEYDI SAMARA</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15232,12 +15232,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>C001386588</t>
+          <t>C001710029</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C001386588 - CAYHUALLA MORALES ESTELA PILAR</t>
+          <t>C001710029 - ANCHANTE RAMIREZ ROSARIO FLORANGEL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15309,12 +15309,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>C001428216</t>
+          <t>C001323273</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>C001428216 - MEZA MENESES NELIDA LUZ</t>
+          <t>C001323273 - ALLCCA ZEGARRA DELIA</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15386,12 +15386,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>C001641578</t>
+          <t>C001386588</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>C001641578 - HERNANDEZ MEZA HEYDI SAMARA</t>
+          <t>C001386588 - CAYHUALLA MORALES ESTELA PILAR</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>C001649862</t>
+          <t>C001533464</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001649862 - SILVA ARRIAGA SUELEN</t>
+          <t>C001533464 - CHACALTANA ESPINOZA DIANA PILAR</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -15605,12 +15605,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>C001533464</t>
+          <t>C001649862</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C001533464 - CHACALTANA ESPINOZA DIANA PILAR</t>
+          <t>C001649862 - SILVA ARRIAGA SUELEN</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
@@ -15670,17 +15670,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>C001430572</t>
+          <t>C001723482</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C001430572 - PACHECO ASCENCIO NAHIRA MARIASELA</t>
+          <t>C001723482 - AQUIJE PINEDA JOSE CARLOS</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H209" s="2" t="n">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
@@ -15708,9 +15708,21 @@
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15735,12 +15747,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>C001723482</t>
+          <t>C000875737</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C001723482 - AQUIJE PINEDA JOSE CARLOS</t>
+          <t>C000875737 - CHUMBES PALOMINO AYME CRISTINA</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15812,17 +15824,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>C000875737</t>
+          <t>C000881245</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C000875737 - CHUMBES PALOMINO AYME CRISTINA</t>
+          <t>C000881245 - CANALES ABREGU MARIA SABINA</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H211" s="2" t="n">
@@ -15835,12 +15847,12 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
@@ -15850,21 +15862,9 @@
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15889,12 +15889,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>C000881245</t>
+          <t>C000881512</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C000881245 - CANALES ABREGU MARIA SABINA</t>
+          <t>C000881512 - VELASQUEZ ESPINOZA CEFERINA</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
@@ -15954,12 +15954,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>C000881512</t>
+          <t>C001430572</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C000881512 - VELASQUEZ ESPINOZA CEFERINA</t>
+          <t>C001430572 - PACHECO ASCENCIO NAHIRA MARIASELA</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -16291,17 +16291,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>C001492348</t>
+          <t>C004237324</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001492348 - CONTRERAS MENDOZA MELVA</t>
+          <t>C004237324 -  ROMERO DIAZ LEHIDY YADHIRA</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -16329,9 +16329,21 @@
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16356,12 +16368,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>C001563548</t>
+          <t>C004176462</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C001563548 - TRINIDAD MUÑOA ROMINA MILAGROS</t>
+          <t>C004176462 - CELIS MAS MARLITH MARGOTH</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16563,17 +16575,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>C004176462</t>
+          <t>C001492348</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C004176462 - CELIS MAS MARLITH MARGOTH</t>
+          <t>C001492348 - CONTRERAS MENDOZA MELVA</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
@@ -16586,12 +16598,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
@@ -16601,21 +16613,9 @@
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P222" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16640,12 +16640,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>C004237324</t>
+          <t>C001563548</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C004237324 -  ROMERO DIAZ LEHIDY YADHIRA</t>
+          <t>C001563548 - TRINIDAD MUÑOA ROMINA MILAGROS</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>C001612683</t>
+          <t>C004020449</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001612683 - ESCATE DE HERNANDEZ LUISA ELSA INOCENTA</t>
+          <t>C004020449 - MEJIA AQUIJE YOLANDA CECILIA</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
@@ -16782,12 +16782,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>C004020449</t>
+          <t>C004030072</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C004020449 - MEJIA AQUIJE YOLANDA CECILIA</t>
+          <t>C004030072 - SANCHEZ UCHUYA YANETT ANGELICA</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -16847,17 +16847,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>C004030072</t>
+          <t>C004020428</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C004030072 - SANCHEZ UCHUYA YANETT ANGELICA</t>
+          <t>C004020428 - RIVERA CONDORI ERIK</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H226" s="2" t="n">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -16885,9 +16885,21 @@
         </is>
       </c>
       <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16912,17 +16924,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>C004020428</t>
+          <t>C001612683</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C004020428 - RIVERA CONDORI ERIK</t>
+          <t>C001612683 - ESCATE DE HERNANDEZ LUISA ELSA INOCENTA</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
@@ -16935,12 +16947,12 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -16950,21 +16962,9 @@
         </is>
       </c>
       <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17362,12 +17362,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>C001752251</t>
+          <t>C001708345</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001752251 - INJANTE DE LA CRUZ MIRELLA DEL ROSARIO.</t>
+          <t>C001708345 - ESCATE HERNANDEZ MALENA HAYDE</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17396,25 +17396,13 @@
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>El vendedor no ofrece diadia</t>
         </is>
       </c>
       <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -17439,12 +17427,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>C001708345</t>
+          <t>C001752251</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001708345 - ESCATE HERNANDEZ MALENA HAYDE</t>
+          <t>C001752251 - INJANTE DE LA CRUZ MIRELLA DEL ROSARIO.</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17473,13 +17461,25 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>El vendedor no ofrece diadia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>C004014409</t>
+          <t>C004142370</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C004014409 - HUASHUAYLLO RAMOS SONIA</t>
+          <t>C004142370 - ORELLANA MORON SONIA BEATRIZ</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17541,11 +17541,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -17585,17 +17581,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>C001752249</t>
+          <t>C004014409</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C001752249 - GUERRA RAMOS GABY GIOVANNA</t>
+          <t>C004014409 - HUASHUAYLLO RAMOS SONIA</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H236" s="2" t="n">
@@ -17608,12 +17604,12 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -17622,10 +17618,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -17650,17 +17662,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>C004060670</t>
+          <t>C001752249</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C004060670 - CARRASCAL PEVE MELISSA JACKELINE</t>
+          <t>C001752249 - GUERRA RAMOS GABY GIOVANNA</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H237" s="2" t="n">
@@ -17673,12 +17685,12 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -17688,21 +17700,9 @@
         </is>
       </c>
       <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>C001735866</t>
+          <t>C004060670</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C001735866 - CCAMA TORRES MARIA FELICIA</t>
+          <t>C004060670 - CARRASCAL PEVE MELISSA JACKELINE</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H238" s="2" t="n">
@@ -17750,12 +17750,12 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -17765,9 +17765,21 @@
         </is>
       </c>
       <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17792,17 +17804,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>C004142370</t>
+          <t>C001735866</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C004142370 - ORELLANA MORON SONIA BEATRIZ</t>
+          <t>C001735866 - CCAMA TORRES MARIA FELICIA</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H239" s="2" t="n">
@@ -17815,12 +17827,12 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L239" t="inlineStr"/>
@@ -17830,21 +17842,9 @@
         </is>
       </c>
       <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -18242,12 +18242,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>C001330256</t>
+          <t>C001215558</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
+          <t>C001215558 -  JIMENEZ ACASIETE MARIELA YANET</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18319,17 +18319,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>C001215558</t>
+          <t>C001534133</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001215558 -  JIMENEZ ACASIETE MARIELA YANET</t>
+          <t>C001534133 - BERROCAL HUAMAN JUANA ROSA</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H246" s="2" t="n">
@@ -18342,12 +18342,12 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
@@ -18357,21 +18357,9 @@
         </is>
       </c>
       <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -18396,17 +18384,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>C001534133</t>
+          <t>C001453033</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C001534133 - BERROCAL HUAMAN JUANA ROSA</t>
+          <t>C001453033 - YALLE CALDERON EDITH MIRIAM</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H247" s="2" t="n">
@@ -18419,12 +18407,12 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L247" t="inlineStr"/>
@@ -18434,9 +18422,21 @@
         </is>
       </c>
       <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -18461,12 +18461,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>C001453033</t>
+          <t>C001500992</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C001453033 - YALLE CALDERON EDITH MIRIAM</t>
+          <t>C001500992 - OLIVARES ROMANI GLORIA</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18538,12 +18538,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>C001500992</t>
+          <t>C001518190</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>C001500992 - OLIVARES ROMANI GLORIA</t>
+          <t>C001518190 - CANCHO ROJAS JUDITH GRISELDA</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18615,12 +18615,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>C001518190</t>
+          <t>C001516381</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>C001518190 - CANCHO ROJAS JUDITH GRISELDA</t>
+          <t>C001516381 - YARMA ECHACCAYA GISSELA</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -18692,12 +18692,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>C001516381</t>
+          <t>C001218188</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>C001516381 - YARMA ECHACCAYA GISSELA</t>
+          <t>C001218188 - REVILLA LARA JOSE LUIS</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -18769,12 +18769,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>C001489520</t>
+          <t>C000872287</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>C001489520 - LUJAN CUAREZ CARLOS VIDAL</t>
+          <t>C000872287 - LARA SALAZAR ISABEL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18846,12 +18846,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>C001549391</t>
+          <t>C001398453</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C001549391 -  MALCA CALVERA PAMELA GEOVANNA</t>
+          <t>C001398453 - ASTOCAZA LUJAN MARIA ELENA</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18923,12 +18923,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>C001398453</t>
+          <t>C000872290</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C001398453 - ASTOCAZA LUJAN MARIA ELENA</t>
+          <t>C000872290 - INCA RAMOS DE QUILLAS VILMA</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19000,17 +19000,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>C001218188</t>
+          <t>C000875789</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>C001218188 - REVILLA LARA JOSE LUIS</t>
+          <t>C000875789 - PAREDES CONDORI NEMIA ELENA</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H255" s="2" t="n">
@@ -19023,12 +19023,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L255" t="inlineStr"/>
@@ -19038,21 +19038,9 @@
         </is>
       </c>
       <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P255" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19077,12 +19065,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>C000872287</t>
+          <t>C001489520</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>C000872287 - LARA SALAZAR ISABEL</t>
+          <t>C001489520 - LUJAN CUAREZ CARLOS VIDAL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19154,12 +19142,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>C000872290</t>
+          <t>C001549391</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C000872290 - INCA RAMOS DE QUILLAS VILMA</t>
+          <t>C001549391 -  MALCA CALVERA PAMELA GEOVANNA</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19231,17 +19219,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>C000875789</t>
+          <t>C001330256</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C000875789 - PAREDES CONDORI NEMIA ELENA</t>
+          <t>C001330256 - GUTIERREZ SANTARIA NATALIA</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H258" s="2" t="n">
@@ -19254,12 +19242,12 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L258" t="inlineStr"/>
@@ -19269,9 +19257,21 @@
         </is>
       </c>
       <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -19296,12 +19296,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>C001492405</t>
+          <t>C001423201</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C001492405 - GONZALES MISARAYME NATALIA</t>
+          <t>C001423201 - SALAZAR HUACCACHI ANDREA YAQUELYN</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19373,17 +19373,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>C001198539</t>
+          <t>C001492405</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C001198539 - TACAS HUANCAHUARI MIRIAM</t>
+          <t>C001492405 - GONZALES MISARAYME NATALIA</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H260" s="2" t="n">
@@ -19396,12 +19396,12 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L260" t="inlineStr"/>
@@ -19411,9 +19411,21 @@
         </is>
       </c>
       <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -19438,17 +19450,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>C000881381</t>
+          <t>C001198539</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C000881381 - GOMEZ GUTIERREZ JULIA FRAXIDES</t>
+          <t>C001198539 - TACAS HUANCAHUARI MIRIAM</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H261" s="2" t="n">
@@ -19461,18 +19473,18 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
-          <t>No desea</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N261" t="inlineStr"/>
@@ -19503,12 +19515,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>C001423201</t>
+          <t>C001102508</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C001423201 - SALAZAR HUACCACHI ANDREA YAQUELYN</t>
+          <t>C001102508 - AVALOS PEREZ WILBER LEONARDO</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19580,12 +19592,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>C001102508</t>
+          <t>C000881381</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C001102508 - AVALOS PEREZ WILBER LEONARDO</t>
+          <t>C000881381 - GOMEZ GUTIERREZ JULIA FRAXIDES</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19614,25 +19626,13 @@
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea</t>
         </is>
       </c>
       <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P263" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q263" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -19657,17 +19657,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>C001584711</t>
+          <t>C001752252</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C001584711 -  HUARCAYA CHANCO FLOR YOVANA</t>
+          <t>C001752252 -  ALCA CUSI VILIA</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H264" s="2" t="n">
@@ -19680,12 +19680,12 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L264" t="inlineStr"/>
@@ -19695,21 +19695,9 @@
         </is>
       </c>
       <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -19811,12 +19799,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>C001708051</t>
+          <t>C001623767</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C001708051 - BAUTISTA BENAVIDES GRISELDA NELIDA</t>
+          <t>C001623767 - GARCIA MAMANI YOVA</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19845,13 +19833,25 @@
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Problemas com el despacho</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -19876,12 +19876,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>C001734420</t>
+          <t>C004042769</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C001734420 - TAPIA URBINA JESICA JOVANA</t>
+          <t>C004042769 -  JUNES ARROYO LUZ HAYDEE</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -19953,12 +19953,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>C004042769</t>
+          <t>C001708051</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>C004042769 -  JUNES ARROYO LUZ HAYDEE</t>
+          <t>C001708051 - BAUTISTA BENAVIDES GRISELDA NELIDA</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -19987,25 +19987,13 @@
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Problemas com el despacho</t>
         </is>
       </c>
       <c r="N268" t="inlineStr"/>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P268" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -20030,17 +20018,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>C001752252</t>
+          <t>C001734420</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C001752252 -  ALCA CUSI VILIA</t>
+          <t>C001734420 - TAPIA URBINA JESICA JOVANA</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H269" s="2" t="n">
@@ -20053,12 +20041,12 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L269" t="inlineStr"/>
@@ -20068,9 +20056,21 @@
         </is>
       </c>
       <c r="N269" t="inlineStr"/>
-      <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -20095,12 +20095,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>C001761938</t>
+          <t>C004165687</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C001761938 - GARAYAR BERNALES CARMEN LUZ</t>
+          <t>C004165687 - QUISPE CUSI VICTORIANO</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20135,7 +20135,7 @@
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -20172,12 +20172,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>C001623767</t>
+          <t>C001716613</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C001623767 - GARCIA MAMANI YOVA</t>
+          <t>C001716613 - SAIRITUPAC MOLINA MIRIAN MAGALY</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20249,12 +20249,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>C004165687</t>
+          <t>C001761938</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C004165687 - QUISPE CUSI VICTORIANO</t>
+          <t>C001761938 - GARAYAR BERNALES CARMEN LUZ</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20289,7 +20289,7 @@
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>C001716613</t>
+          <t>C000872160</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001716613 - SAIRITUPAC MOLINA MIRIAN MAGALY</t>
+          <t>C000872160 - QUISPE ABURTO GABY VICTORIA</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20363,7 +20363,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O273" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -20403,12 +20407,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>C000872160</t>
+          <t>C004161370</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C000872160 - QUISPE ABURTO GABY VICTORIA</t>
+          <t>C004161370 - RAMIREZ LLOCLLA KANDY YOVANA</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20440,11 +20444,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
           <t>Muy dispuesto</t>
@@ -20484,12 +20484,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>C004029978</t>
+          <t>C004161347</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C004029978 - LLAMOCCA ATAUJE DORA</t>
+          <t>C004161347 - CCORA SOTO AYDEE</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20561,12 +20561,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>C004161370</t>
+          <t>C004029978</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C004161370 - RAMIREZ LLOCLLA KANDY YOVANA</t>
+          <t>C004029978 - LLAMOCCA ATAUJE DORA</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>C004161347</t>
+          <t>C001584711</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C004161347 - CCORA SOTO AYDEE</t>
+          <t>C001584711 -  HUARCAYA CHANCO FLOR YOVANA</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20922,12 +20922,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>C004042768</t>
+          <t>C001568416</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C004042768 - ACHAMISO ARONI ESTEFANY MARIBEL</t>
+          <t>C001568416 - FARFAN DE MORON CARMEN GLORIA</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -20999,12 +20999,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>C004176366</t>
+          <t>C001478173</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C004176366 - ARAUJO TORRES DE LAGOS ELSA</t>
+          <t>C001478173 - GUTIERREZ DAVALOS JOHANA MARITZA</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21076,12 +21076,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>C004181577</t>
+          <t>C004101290</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C004181577 - MORALES ROJAS JACQUELINE CLARA</t>
+          <t>C004101290 - RAMOS DELGADO MAURA ALEJANDRA</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21110,13 +21110,25 @@
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
-          <t>No desea el app</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -21141,12 +21153,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>C004165675</t>
+          <t>C004042768</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C004165675 - HUACCACHI POMA DIANE</t>
+          <t>C004042768 - ACHAMISO ARONI ESTEFANY MARIBEL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21218,12 +21230,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>C001478173</t>
+          <t>C004176366</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C001478173 - GUTIERREZ DAVALOS JOHANA MARITZA</t>
+          <t>C004176366 - ARAUJO TORRES DE LAGOS ELSA</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21295,12 +21307,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>C004101290</t>
+          <t>C004181577</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C004101290 - RAMOS DELGADO MAURA ALEJANDRA</t>
+          <t>C004181577 - MORALES ROJAS JACQUELINE CLARA</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21329,25 +21341,13 @@
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No desea el app</t>
         </is>
       </c>
       <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>C001568416</t>
+          <t>C004165675</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C001568416 - FARFAN DE MORON CARMEN GLORIA</t>
+          <t>C004165675 - HUACCACHI POMA DIANE</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21757,17 +21757,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>C001492576</t>
+          <t>C001622444</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001492576 - PAIMA GARCIA TOMASA DE JESUS</t>
+          <t>C001622444 - SUMARI QUISPE JURICA JANETT</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H292" s="2" t="n">
@@ -21780,12 +21780,12 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L292" t="inlineStr"/>
@@ -21795,9 +21795,21 @@
         </is>
       </c>
       <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="inlineStr"/>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -21822,17 +21834,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>C001622444</t>
+          <t>C001492576</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C001622444 - SUMARI QUISPE JURICA JANETT</t>
+          <t>C001492576 - PAIMA GARCIA TOMASA DE JESUS</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H293" s="2" t="n">
@@ -21845,12 +21857,12 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L293" t="inlineStr"/>
@@ -21860,21 +21872,9 @@
         </is>
       </c>
       <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -21899,12 +21899,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>C004240818</t>
+          <t>C004200425</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
+          <t>C004200425 - AURIS MELGAR MARLENE ELIZABETH</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -21976,12 +21976,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>C004200425</t>
+          <t>C004240818</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>C004200425 - AURIS MELGAR MARLENE ELIZABETH</t>
+          <t>C004240818 - DONAYRE PACHECO GAUDY VALERIA</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22207,12 +22207,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>C001721510</t>
+          <t>C001649207</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001721510 - PALACIOS LLOCLLA RITA CARMEN</t>
+          <t>C001649207 - FAJARDO ANCAYA ZOILA MILAGROS</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22257,7 +22257,7 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -22284,12 +22284,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>C001649207</t>
+          <t>C001721510</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001649207 - FAJARDO ANCAYA ZOILA MILAGROS</t>
+          <t>C001721510 - PALACIOS LLOCLLA RITA CARMEN</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -23265,12 +23265,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>C000875513</t>
+          <t>C001385265</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>C000875513 - MENDOZA LIZANO PAULINA</t>
+          <t>C001385265 - GARCIA FARFAN MARGARITA ESTELA</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -23299,17 +23299,25 @@
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Tieme iphone</t>
-        </is>
-      </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -23334,12 +23342,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>C001709603</t>
+          <t>C001218181</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>C001709603 - CARDENAS GUTIERREZ LIDIA ALEJANDRA</t>
+          <t>C001218181 - QUISPE HUAMANI OSCAR JOSE MANUEL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23411,12 +23419,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>C001385265</t>
+          <t>C001709606</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>C001385265 - GARCIA FARFAN MARGARITA ESTELA</t>
+          <t>C001709606 - FLORES MORON MARIA ESPERANZA</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23461,7 +23469,7 @@
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
     </row>
@@ -23488,12 +23496,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>C001709606</t>
+          <t>C000875513</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>C001709606 - FLORES MORON MARIA ESPERANZA</t>
+          <t>C000875513 - MENDOZA LIZANO PAULINA</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23522,25 +23530,17 @@
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N315" t="inlineStr"/>
-      <c r="O315" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P315" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+          <t>Tieme iphone</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -23565,12 +23565,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>C001218181</t>
+          <t>C001709603</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C001218181 - QUISPE HUAMANI OSCAR JOSE MANUEL</t>
+          <t>C001709603 - CARDENAS GUTIERREZ LIDIA ALEJANDRA</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -24291,17 +24291,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>C001506204</t>
+          <t>C001197394</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>C001506204 - ESTACION EL OVALO E.I.R.L.</t>
+          <t>C001197394 - BAUTISTA LEON REYNA BEATRIZ</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H326" s="2" t="n">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L326" t="inlineStr"/>
@@ -24329,9 +24329,21 @@
         </is>
       </c>
       <c r="N326" t="inlineStr"/>
-      <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="inlineStr"/>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -24356,12 +24368,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>C001197394</t>
+          <t>C001360879</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>C001197394 - BAUTISTA LEON REYNA BEATRIZ</t>
+          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -24433,17 +24445,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>C001360879</t>
+          <t>C001506204</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>C001360879 - OYOLO LLAMOCCA FAUSTA DELIA</t>
+          <t>C001506204 - ESTACION EL OVALO E.I.R.L.</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H328" s="2" t="n">
@@ -24456,12 +24468,12 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L328" t="inlineStr"/>
@@ -24471,21 +24483,9 @@
         </is>
       </c>
       <c r="N328" t="inlineStr"/>
-      <c r="O328" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P328" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -25439,12 +25439,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>C004196959</t>
+          <t>C004033260</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>C004196959 - SARAVIA HERNANDEZ LEONOR JESUS</t>
+          <t>C004033260 - BERNAOLA AYQUIPA RENZO JESUS</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25516,12 +25516,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>C004033260</t>
+          <t>C004196959</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>C004033260 - BERNAOLA AYQUIPA RENZO JESUS</t>
+          <t>C004196959 - SARAVIA HERNANDEZ LEONOR JESUS</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -25593,12 +25593,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>C004192518</t>
+          <t>C001612448</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>C004192518 - LEON HERNANDEZ KIHARA RUBY</t>
+          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25670,12 +25670,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>C001612448</t>
+          <t>C001481930</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>C001612448 - HERNANDEZ SOTO PATRICIA ROSA</t>
+          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25747,12 +25747,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>C001481930</t>
+          <t>C004192518</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>C001481930 - FARFAN QUIROZ NARDA UCELLY</t>
+          <t>C004192518 - LEON HERNANDEZ KIHARA RUBY</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -27183,17 +27183,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>C000881475</t>
+          <t>C001705169</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>C000881475 - CARDENAS CLAUDIO OFELIA LUISA</t>
+          <t>C001705169 - DIAZ DE LA TORRE MARIAFERNANDA</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H366" s="2" t="n">
@@ -27206,12 +27206,12 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L366" t="inlineStr"/>
@@ -27221,21 +27221,9 @@
         </is>
       </c>
       <c r="N366" t="inlineStr"/>
-      <c r="O366" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P366" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q366" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O366" t="inlineStr"/>
+      <c r="P366" t="inlineStr"/>
+      <c r="Q366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -27260,17 +27248,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>C000881526</t>
+          <t>C000881475</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>C000881526 - SAN BOSCO E.I.R.L.</t>
+          <t>C000881475 - CARDENAS CLAUDIO OFELIA LUISA</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H367" s="2" t="n">
@@ -27283,12 +27271,12 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L367" t="inlineStr"/>
@@ -27298,9 +27286,21 @@
         </is>
       </c>
       <c r="N367" t="inlineStr"/>
-      <c r="O367" t="inlineStr"/>
-      <c r="P367" t="inlineStr"/>
-      <c r="Q367" t="inlineStr"/>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -27325,17 +27325,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>C001016278</t>
+          <t>C000881526</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>C001016278 - UNZUETA DE CHAVEZ HILDA ROSALIA</t>
+          <t>C000881526 - SAN BOSCO E.I.R.L.</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H368" s="2" t="n">
@@ -27348,12 +27348,12 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L368" t="inlineStr"/>
@@ -27363,21 +27363,9 @@
         </is>
       </c>
       <c r="N368" t="inlineStr"/>
-      <c r="O368" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P368" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q368" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -27402,12 +27390,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>C001559354</t>
+          <t>C001016278</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>C001559354 - DONGO ROQUE ANAI TERESA</t>
+          <t>C001016278 - UNZUETA DE CHAVEZ HILDA ROSALIA</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -27479,12 +27467,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>C001559351</t>
+          <t>C001559354</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>C001559351 - DE LA ROSA AZURZA BERTHA</t>
+          <t>C001559354 - DONGO ROQUE ANAI TERESA</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -27556,12 +27544,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>C001674222</t>
+          <t>C001559351</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>C001674222 - SALCEDO ESPARZA DAVID LUIS</t>
+          <t>C001559351 - DE LA ROSA AZURZA BERTHA</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -27633,12 +27621,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>C000881331</t>
+          <t>C001674222</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>C000881331 - ROSALES ESCOBAR JUANA IRIS</t>
+          <t>C001674222 - SALCEDO ESPARZA DAVID LUIS</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -27710,12 +27698,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>C000882018</t>
+          <t>C000881331</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>C000882018 - AYALA DE CAVERO GENARA</t>
+          <t>C000881331 - ROSALES ESCOBAR JUANA IRIS</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -27787,17 +27775,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>C001708048</t>
+          <t>C000882018</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>C001708048 - CONDORI RIVERA MARIA CLARED</t>
+          <t>C000882018 - AYALA DE CAVERO GENARA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H374" s="2" t="n">
@@ -27810,12 +27798,12 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L374" t="inlineStr"/>
@@ -27825,9 +27813,21 @@
         </is>
       </c>
       <c r="N374" t="inlineStr"/>
-      <c r="O374" t="inlineStr"/>
-      <c r="P374" t="inlineStr"/>
-      <c r="Q374" t="inlineStr"/>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -27852,12 +27852,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>C001705169</t>
+          <t>C001708048</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>C001705169 - DIAZ DE LA TORRE MARIAFERNANDA</t>
+          <t>C001708048 - CONDORI RIVERA MARIA CLARED</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L375" t="inlineStr"/>
@@ -28278,17 +28278,17 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>C001405735</t>
+          <t>C001492696</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>C001405735 - GARCIA VILLANUEVA BETTY MERCEDES</t>
+          <t>C001492696 - VARGAS JURADO CHARITO ANYELLY</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H381" s="2" t="n">
@@ -28301,12 +28301,12 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L381" t="inlineStr"/>
@@ -28316,9 +28316,21 @@
         </is>
       </c>
       <c r="N381" t="inlineStr"/>
-      <c r="O381" t="inlineStr"/>
-      <c r="P381" t="inlineStr"/>
-      <c r="Q381" t="inlineStr"/>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -28343,12 +28355,12 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>C001492696</t>
+          <t>C001710219</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>C001492696 - VARGAS JURADO CHARITO ANYELLY</t>
+          <t>C001710219 - ESCALANTE LAGOS GERARDO JESUS</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -28420,17 +28432,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>C001710219</t>
+          <t>C001733234</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>C001710219 - ESCALANTE LAGOS GERARDO JESUS</t>
+          <t>C001733234 -  VALENCIA ALVARADO MARICRUZ ROSARIO</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H383" s="2" t="n">
@@ -28443,12 +28455,12 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L383" t="inlineStr"/>
@@ -28458,21 +28470,9 @@
         </is>
       </c>
       <c r="N383" t="inlineStr"/>
-      <c r="O383" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P383" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q383" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr"/>
+      <c r="Q383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -28497,12 +28497,12 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>C001733234</t>
+          <t>C001405735</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>C001733234 -  VALENCIA ALVARADO MARICRUZ ROSARIO</t>
+          <t>C001405735 - GARCIA VILLANUEVA BETTY MERCEDES</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -28525,7 +28525,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L384" t="inlineStr"/>
@@ -28846,12 +28846,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>C001683409</t>
+          <t>C000881799</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>C001683409 - MEDRANO SAAVEDRA YANINA</t>
+          <t>C000881799 - BLONDET ALTAMIRANO MARLENI ESMERALDA</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -28923,12 +28923,12 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>C001539717</t>
+          <t>C001683409</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
+          <t>C001683409 - MEDRANO SAAVEDRA YANINA</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -29000,12 +29000,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>C001103760</t>
+          <t>C001539717</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>C001103760 - BARRIGA LUQUE DE CARO ELSA NERY</t>
+          <t>C001539717 - QUISPE QUIHUE ABIGAIL NANCY</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -29077,12 +29077,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>C001161299</t>
+          <t>C001103760</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>C001161299 - PARADO PEREZ SANTA BENITA</t>
+          <t>C001103760 - BARRIGA LUQUE DE CARO ELSA NERY</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -29154,12 +29154,12 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>C000875016</t>
+          <t>C001161299</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>C000875016 - CHALCO CASTA EDA NELY ELENA</t>
+          <t>C001161299 - PARADO PEREZ SANTA BENITA</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -29231,12 +29231,12 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>C000881799</t>
+          <t>C000875016</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>C000881799 - BLONDET ALTAMIRANO MARLENI ESMERALDA</t>
+          <t>C000875016 - CHALCO CASTA EDA NELY ELENA</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -30865,17 +30865,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>C004178774</t>
+          <t>C004172312</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>C004178774 - ESPINOZA QUIJANDRIA CARLOS MARTIN</t>
+          <t>C004172312 - CHECCLLO BORDA ALEXANDRA KATERINE</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H416" s="2" t="n">
@@ -30888,12 +30888,12 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L416" t="inlineStr"/>
@@ -30903,21 +30903,9 @@
         </is>
       </c>
       <c r="N416" t="inlineStr"/>
-      <c r="O416" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P416" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q416" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -30942,17 +30930,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>C004172312</t>
+          <t>C004178774</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>C004172312 - CHECCLLO BORDA ALEXANDRA KATERINE</t>
+          <t>C004178774 - ESPINOZA QUIJANDRIA CARLOS MARTIN</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H417" s="2" t="n">
@@ -30965,12 +30953,12 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L417" t="inlineStr"/>
@@ -30980,9 +30968,21 @@
         </is>
       </c>
       <c r="N417" t="inlineStr"/>
-      <c r="O417" t="inlineStr"/>
-      <c r="P417" t="inlineStr"/>
-      <c r="Q417" t="inlineStr"/>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -31587,12 +31587,12 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>C001520676</t>
+          <t>C001493961</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>C001520676 - BRICENO MAYTA JACQUELINE KARIN</t>
+          <t>C001493961 - LICLA TOMAYRO CARMEN ROSA</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L426" t="inlineStr"/>
@@ -31652,12 +31652,12 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>C001493961</t>
+          <t>C001497131</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>C001493961 - LICLA TOMAYRO CARMEN ROSA</t>
+          <t>C001497131 - MARTINEZ CASTILLO MARIA FERNANDA</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L427" t="inlineStr"/>
@@ -31717,12 +31717,12 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>C001497131</t>
+          <t>C001520676</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>C001497131 - MARTINEZ CASTILLO MARIA FERNANDA</t>
+          <t>C001520676 - BRICENO MAYTA JACQUELINE KARIN</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -33250,12 +33250,12 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>C001576847</t>
+          <t>C001563658</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>C001576847 - HUAMANI ARANGOITIA LUCERO ABIHAIL</t>
+          <t>C001563658 - DE LA CRUZ MORALES DE ALVITES DINA MARGA</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -33284,13 +33284,25 @@
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>No es la titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N449" t="inlineStr"/>
-      <c r="O449" t="inlineStr"/>
-      <c r="P449" t="inlineStr"/>
-      <c r="Q449" t="inlineStr"/>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -33315,17 +33327,17 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>C001638974</t>
+          <t>C001549323</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>C001638974 - RAMIREZ GARCIA CAMILA PAOLA</t>
+          <t>C001549323 - NAVARRO CRUZ BETTY</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H450" s="2" t="n">
@@ -33338,12 +33350,12 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L450" t="inlineStr"/>
@@ -33353,21 +33365,9 @@
         </is>
       </c>
       <c r="N450" t="inlineStr"/>
-      <c r="O450" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P450" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q450" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O450" t="inlineStr"/>
+      <c r="P450" t="inlineStr"/>
+      <c r="Q450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -33392,17 +33392,17 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>C001549323</t>
+          <t>C001638974</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>C001549323 - NAVARRO CRUZ BETTY</t>
+          <t>C001638974 - RAMIREZ GARCIA CAMILA PAOLA</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H451" s="2" t="n">
@@ -33415,12 +33415,12 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L451" t="inlineStr"/>
@@ -33430,9 +33430,21 @@
         </is>
       </c>
       <c r="N451" t="inlineStr"/>
-      <c r="O451" t="inlineStr"/>
-      <c r="P451" t="inlineStr"/>
-      <c r="Q451" t="inlineStr"/>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -33457,12 +33469,12 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>C001563658</t>
+          <t>C001576847</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>C001563658 - DE LA CRUZ MORALES DE ALVITES DINA MARGA</t>
+          <t>C001576847 - HUAMANI ARANGOITIA LUCERO ABIHAIL</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -33491,25 +33503,13 @@
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es la titular</t>
         </is>
       </c>
       <c r="N452" t="inlineStr"/>
-      <c r="O452" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P452" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q452" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O452" t="inlineStr"/>
+      <c r="P452" t="inlineStr"/>
+      <c r="Q452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -33830,17 +33830,17 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>C001748378</t>
+          <t>C001734139</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>C001748378 - FARFAN CHILON FATIMA SARITA</t>
+          <t>C001734139 - ROJAS CISTERNAS MASIEL HOLAYA</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H457" s="2" t="n">
@@ -33853,12 +33853,12 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L457" t="inlineStr"/>
@@ -33868,21 +33868,9 @@
         </is>
       </c>
       <c r="N457" t="inlineStr"/>
-      <c r="O457" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P457" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q457" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O457" t="inlineStr"/>
+      <c r="P457" t="inlineStr"/>
+      <c r="Q457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -33907,12 +33895,12 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>C001748916</t>
+          <t>C001552894</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
+          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -33984,12 +33972,12 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>C004025529</t>
+          <t>C001748378</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>C004025529 - EL BATAN DEL NORTE E.I.R.L.</t>
+          <t>C001748378 - FARFAN CHILON FATIMA SARITA</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -34061,17 +34049,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>C001734139</t>
+          <t>C001748916</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>C001734139 - ROJAS CISTERNAS MASIEL HOLAYA</t>
+          <t>C001748916 - CUSQUISIBAN QUISPE MARIA MARCELINA</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H460" s="2" t="n">
@@ -34084,12 +34072,12 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L460" t="inlineStr"/>
@@ -34099,9 +34087,21 @@
         </is>
       </c>
       <c r="N460" t="inlineStr"/>
-      <c r="O460" t="inlineStr"/>
-      <c r="P460" t="inlineStr"/>
-      <c r="Q460" t="inlineStr"/>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -34126,12 +34126,12 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>C001552894</t>
+          <t>C004025529</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>C001552894 - INVERSIONES &amp; TIENDAS ROJAS E.I.R.L.</t>
+          <t>C004025529 - EL BATAN DEL NORTE E.I.R.L.</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -34203,12 +34203,12 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>C001362233</t>
+          <t>C000875203</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>C001362233 - SAAVEDRA SOTO JAVIER YSIDRO</t>
+          <t>C000875203 - ROSAS NIETO JUAN</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -34280,12 +34280,12 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>C001069416</t>
+          <t>C000875219</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>C001069416 - CUCHO MITACC GABILU MILAGROS</t>
+          <t>C000875219 - ROMAN VILCAS MARIA MONICA</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -34314,25 +34314,13 @@
       <c r="L463" t="inlineStr"/>
       <c r="M463" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona de tercera edad</t>
         </is>
       </c>
       <c r="N463" t="inlineStr"/>
-      <c r="O463" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P463" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q463" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O463" t="inlineStr"/>
+      <c r="P463" t="inlineStr"/>
+      <c r="Q463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -34357,17 +34345,17 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>C000875203</t>
+          <t>C000875549</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>C000875203 - ROSAS NIETO JUAN</t>
+          <t>C000875549 - SABASTIZAGAL CAMPOS LUZ NORA</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H464" s="2" t="n">
@@ -34380,12 +34368,12 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L464" t="inlineStr"/>
@@ -34395,21 +34383,9 @@
         </is>
       </c>
       <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P464" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q464" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O464" t="inlineStr"/>
+      <c r="P464" t="inlineStr"/>
+      <c r="Q464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -34434,12 +34410,12 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>C000875219</t>
+          <t>C000875926</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>C000875219 - ROMAN VILCAS MARIA MONICA</t>
+          <t>C000875926 - QUISPE CACERES DORIS</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -34468,13 +34444,25 @@
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Persona de tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N465" t="inlineStr"/>
-      <c r="O465" t="inlineStr"/>
-      <c r="P465" t="inlineStr"/>
-      <c r="Q465" t="inlineStr"/>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -34499,17 +34487,17 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>C000875549</t>
+          <t>C001069416</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>C000875549 - SABASTIZAGAL CAMPOS LUZ NORA</t>
+          <t>C001069416 - CUCHO MITACC GABILU MILAGROS</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H466" s="2" t="n">
@@ -34522,12 +34510,12 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L466" t="inlineStr"/>
@@ -34537,9 +34525,21 @@
         </is>
       </c>
       <c r="N466" t="inlineStr"/>
-      <c r="O466" t="inlineStr"/>
-      <c r="P466" t="inlineStr"/>
-      <c r="Q466" t="inlineStr"/>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -34564,12 +34564,12 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>C000875926</t>
+          <t>C001362233</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>C000875926 - QUISPE CACERES DORIS</t>
+          <t>C001362233 - SAAVEDRA SOTO JAVIER YSIDRO</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -34641,12 +34641,12 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>C004216987</t>
+          <t>C004243810</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>C004216987 - BENAVIDES SOTO LIDIA ROCIO</t>
+          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -34795,12 +34795,12 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>C004243810</t>
+          <t>C004216987</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>C004243810 - ORE CURI CARMEN JENNIFER</t>
+          <t>C004216987 - BENAVIDES SOTO LIDIA ROCIO</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -34872,17 +34872,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>C004199676</t>
+          <t>C004207402</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>C004199676 - QUINTANA ROJAS XIOMARA YULIANA</t>
+          <t>C004207402 - COLLADO AROSTIGUE MONICA FELICITA</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H471" s="2" t="n">
@@ -34895,12 +34895,12 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L471" t="inlineStr"/>
@@ -34910,9 +34910,21 @@
         </is>
       </c>
       <c r="N471" t="inlineStr"/>
-      <c r="O471" t="inlineStr"/>
-      <c r="P471" t="inlineStr"/>
-      <c r="Q471" t="inlineStr"/>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -34937,17 +34949,17 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>C004207402</t>
+          <t>C004199676</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>C004207402 - COLLADO AROSTIGUE MONICA FELICITA</t>
+          <t>C004199676 - QUINTANA ROJAS XIOMARA YULIANA</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H472" s="2" t="n">
@@ -34960,12 +34972,12 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L472" t="inlineStr"/>
@@ -34975,21 +34987,9 @@
         </is>
       </c>
       <c r="N472" t="inlineStr"/>
-      <c r="O472" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P472" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q472" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O472" t="inlineStr"/>
+      <c r="P472" t="inlineStr"/>
+      <c r="Q472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -36312,12 +36312,12 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>C001471930</t>
+          <t>C004191301</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>C001471930 - VICUNA REYES RAMON LINO</t>
+          <t>C004191301 - SARAVIA FLORES GRACIELA</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -36389,12 +36389,12 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>C004191301</t>
+          <t>C004191304</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>C004191301 - SARAVIA FLORES GRACIELA</t>
+          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -36466,12 +36466,12 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>C004191304</t>
+          <t>C001471930</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>C004191304 - SARAVIA TORRES HECTOR LUIS</t>
+          <t>C001471930 - VICUNA REYES RAMON LINO</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -36851,12 +36851,12 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>C000882854</t>
+          <t>C001374929</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>C000882854 - RODRIGUEZ TORRES JANETT</t>
+          <t>C001374929 - GALINDO HUARANCCA DIANA YSABEL</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -36928,12 +36928,12 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>C000874379</t>
+          <t>C000882854</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>C000874379 - COOP SERV MULT INTEGRACION MAGISTERIAL</t>
+          <t>C000882854 - RODRIGUEZ TORRES JANETT</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -37005,12 +37005,12 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>C000872477</t>
+          <t>C000882632</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
+          <t>C000882632 - RAMIREZ VICU A JULIA</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -37082,12 +37082,12 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>C000882632</t>
+          <t>C000882129</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>C000882632 - RAMIREZ VICU A JULIA</t>
+          <t>C000882129 - EL GOLFO SAC</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -37159,17 +37159,17 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>C000882129</t>
+          <t>C000881560</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>C000882129 - EL GOLFO SAC</t>
+          <t>C000881560 - SAAVEDRA AGUILAR EDITH ESTELA</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H502" s="2" t="n">
@@ -37182,12 +37182,12 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L502" t="inlineStr"/>
@@ -37197,21 +37197,9 @@
         </is>
       </c>
       <c r="N502" t="inlineStr"/>
-      <c r="O502" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P502" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q502" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O502" t="inlineStr"/>
+      <c r="P502" t="inlineStr"/>
+      <c r="Q502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -37236,17 +37224,17 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>C000881560</t>
+          <t>C000881032</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>C000881560 - SAAVEDRA AGUILAR EDITH ESTELA</t>
+          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H503" s="2" t="n">
@@ -37259,12 +37247,12 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L503" t="inlineStr"/>
@@ -37274,9 +37262,21 @@
         </is>
       </c>
       <c r="N503" t="inlineStr"/>
-      <c r="O503" t="inlineStr"/>
-      <c r="P503" t="inlineStr"/>
-      <c r="Q503" t="inlineStr"/>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -37301,12 +37301,12 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>C000881032</t>
+          <t>C000874379</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>C000881032 - HUAMAN BAUTISTA ANDRES</t>
+          <t>C000874379 - COOP SERV MULT INTEGRACION MAGISTERIAL</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -37378,12 +37378,12 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>C001448001</t>
+          <t>C000872477</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
+          <t>C000872477 - CHANCA BELLIDO LEONIDAS</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -37455,12 +37455,12 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>C001374929</t>
+          <t>C001448001</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>C001374929 - GALINDO HUARANCCA DIANA YSABEL</t>
+          <t>C001448001 - ROMAN MANTARI MARILU ISABEL</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -37751,12 +37751,12 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>C004205639</t>
+          <t>C004189020</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>C004205639 - NIEVES OQUEÑA LILIANA</t>
+          <t>C004189020 - HUAMAN VARGAS ENMA</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -37828,12 +37828,12 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>C004189020</t>
+          <t>C004205639</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>C004189020 - HUAMAN VARGAS ENMA</t>
+          <t>C004205639 - NIEVES OQUEÑA LILIANA</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
